--- a/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
@@ -617,10 +617,10 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>13.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43.59</v>
+        <v>38.79</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>53.67</v>
+        <v>48.87</v>
       </c>
       <c r="H27" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>54.21</v>
+        <v>49.36</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
@@ -539,10 +539,10 @@
         <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="H10" t="n">
-        <v>24.2</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="11">
@@ -643,10 +643,10 @@
         <v>0.12</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>38.79</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>48.87</v>
+        <v>55.06</v>
       </c>
       <c r="H27" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>49.36</v>
+        <v>55.61</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 15 Herrería, carpintería y vidrios</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Rejas, portones y herrería</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
@@ -810,7 +810,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MO-OF1-SOLD</t>
+          <t>MO-OF1-PISOD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-04-030.xlsx
@@ -810,7 +810,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MO-OF1-PISOD</t>
+          <t>MO-OF1-SOLD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
